--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92542890173</v>
+        <v>46157.93118801935</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93118801935</v>
+        <v>46157.93370332957</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93370332957</v>
+        <v>46157.93675095728</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93675095728</v>
+        <v>46158.28196366757</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28196366757</v>
+        <v>46158.29721225781</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29721225781</v>
+        <v>46158.29793129019</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29793129019</v>
+        <v>46158.33357763549</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33357763549</v>
+        <v>46158.37212009984</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2024/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37212009984</v>
+        <v>46158.3726889869</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
